--- a/input/timetable/ИВТ_.xlsx
+++ b/input/timetable/ИВТ_.xlsx
@@ -1541,24 +1541,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1568,146 +1550,117 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1729,6 +1682,12 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1744,115 +1703,117 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1861,77 +1822,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1942,6 +1833,87 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1955,16 +1927,28 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1976,61 +1960,113 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2040,42 +2076,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2108,59 +2108,84 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2169,9 +2194,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2188,39 +2210,17 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Нейтральный" xfId="2" builtinId="28"/>
@@ -2698,10 +2698,10 @@
       <c r="A7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="142" t="s">
+      <c r="C7" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="142"/>
+      <c r="D7" s="121"/>
       <c r="E7" s="15" t="s">
         <v>86</v>
       </c>
@@ -2711,10 +2711,10 @@
       <c r="G7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="142" t="s">
+      <c r="I7" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="142"/>
+      <c r="J7" s="121"/>
       <c r="K7" s="15" t="s">
         <v>87</v>
       </c>
@@ -2724,19 +2724,19 @@
     </row>
     <row r="8" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12"/>
-      <c r="C8" s="152" t="s">
+      <c r="C8" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="152"/>
-      <c r="E8" s="152"/>
-      <c r="F8" s="152"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
       <c r="G8" s="12"/>
-      <c r="I8" s="152" t="s">
+      <c r="I8" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="J8" s="152"/>
-      <c r="K8" s="152"/>
-      <c r="L8" s="152"/>
+      <c r="J8" s="131"/>
+      <c r="K8" s="131"/>
+      <c r="L8" s="131"/>
     </row>
     <row r="9" spans="1:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
@@ -2771,86 +2771,86 @@
       <c r="B10" s="24">
         <v>1</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="D10" s="80"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="81"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="75"/>
       <c r="G10" s="23" t="s">
         <v>18</v>
       </c>
       <c r="H10" s="24">
         <v>1</v>
       </c>
-      <c r="I10" s="79" t="s">
+      <c r="I10" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="80"/>
-      <c r="K10" s="80"/>
-      <c r="L10" s="81"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="75"/>
     </row>
     <row r="11" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="25"/>
       <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="132" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="153" t="s">
+      <c r="D11" s="133"/>
+      <c r="E11" s="134" t="s">
         <v>93</v>
       </c>
-      <c r="F11" s="154"/>
+      <c r="F11" s="135"/>
       <c r="G11" s="25"/>
       <c r="H11" s="26">
         <v>2</v>
       </c>
-      <c r="I11" s="82"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="84"/>
+      <c r="I11" s="167"/>
+      <c r="J11" s="168"/>
+      <c r="K11" s="168"/>
+      <c r="L11" s="169"/>
     </row>
     <row r="12" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
       <c r="B12" s="26">
         <v>3</v>
       </c>
-      <c r="C12" s="99" t="s">
+      <c r="C12" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="100"/>
-      <c r="E12" s="100" t="s">
+      <c r="D12" s="86"/>
+      <c r="E12" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="101"/>
+      <c r="F12" s="92"/>
       <c r="G12" s="25"/>
       <c r="H12" s="26">
         <v>3</v>
       </c>
-      <c r="I12" s="155"/>
-      <c r="J12" s="156"/>
-      <c r="K12" s="156"/>
-      <c r="L12" s="157"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="137"/>
+      <c r="K12" s="137"/>
+      <c r="L12" s="138"/>
     </row>
     <row r="13" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="27"/>
       <c r="B13" s="28">
         <v>4</v>
       </c>
-      <c r="C13" s="143"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="145"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="123"/>
+      <c r="F13" s="124"/>
       <c r="G13" s="27"/>
       <c r="H13" s="28">
         <v>4</v>
       </c>
-      <c r="I13" s="143"/>
-      <c r="J13" s="144"/>
-      <c r="K13" s="144"/>
-      <c r="L13" s="145"/>
+      <c r="I13" s="122"/>
+      <c r="J13" s="123"/>
+      <c r="K13" s="123"/>
+      <c r="L13" s="124"/>
     </row>
     <row r="14" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="29" t="s">
@@ -2859,94 +2859,94 @@
       <c r="B14" s="30">
         <v>1</v>
       </c>
-      <c r="C14" s="149" t="s">
+      <c r="C14" s="128" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="150"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="151"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="130"/>
       <c r="G14" s="29" t="s">
         <v>19</v>
       </c>
       <c r="H14" s="30">
         <v>1</v>
       </c>
-      <c r="I14" s="146" t="s">
+      <c r="I14" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="J14" s="147"/>
-      <c r="K14" s="147"/>
-      <c r="L14" s="148"/>
+      <c r="J14" s="126"/>
+      <c r="K14" s="126"/>
+      <c r="L14" s="127"/>
     </row>
     <row r="15" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="25"/>
       <c r="B15" s="26">
         <v>2</v>
       </c>
-      <c r="C15" s="113" t="s">
+      <c r="C15" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="114"/>
-      <c r="E15" s="114" t="s">
+      <c r="D15" s="87"/>
+      <c r="E15" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="115"/>
+      <c r="F15" s="88"/>
       <c r="G15" s="25"/>
       <c r="H15" s="26">
         <v>2</v>
       </c>
-      <c r="I15" s="73" t="s">
+      <c r="I15" s="132" t="s">
         <v>97</v>
       </c>
-      <c r="J15" s="74"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="75"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="163"/>
     </row>
     <row r="16" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
         <v>3</v>
       </c>
-      <c r="C16" s="99" t="s">
+      <c r="C16" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="100"/>
-      <c r="E16" s="100" t="s">
+      <c r="D16" s="86"/>
+      <c r="E16" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="101"/>
+      <c r="F16" s="92"/>
       <c r="G16" s="25"/>
       <c r="H16" s="26">
         <v>3</v>
       </c>
-      <c r="I16" s="99" t="s">
+      <c r="I16" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="J16" s="100"/>
-      <c r="K16" s="100"/>
-      <c r="L16" s="101"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="92"/>
     </row>
     <row r="17" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="49"/>
       <c r="B17" s="46">
         <v>5</v>
       </c>
-      <c r="C17" s="159" t="s">
+      <c r="C17" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="160"/>
-      <c r="E17" s="160"/>
-      <c r="F17" s="161"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="117"/>
       <c r="G17" s="31"/>
       <c r="H17" s="28">
         <v>4</v>
       </c>
-      <c r="I17" s="94" t="s">
+      <c r="I17" s="173" t="s">
         <v>96</v>
       </c>
-      <c r="J17" s="95"/>
-      <c r="K17" s="95"/>
-      <c r="L17" s="96"/>
+      <c r="J17" s="174"/>
+      <c r="K17" s="174"/>
+      <c r="L17" s="175"/>
     </row>
     <row r="18" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="29" t="s">
@@ -2955,88 +2955,88 @@
       <c r="B18" s="30">
         <v>2</v>
       </c>
-      <c r="C18" s="162" t="s">
+      <c r="C18" s="103" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="163"/>
-      <c r="E18" s="163"/>
-      <c r="F18" s="164"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="105"/>
       <c r="G18" s="29" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="30">
         <v>1</v>
       </c>
-      <c r="I18" s="91" t="s">
+      <c r="I18" s="170" t="s">
         <v>99</v>
       </c>
-      <c r="J18" s="92"/>
-      <c r="K18" s="92"/>
-      <c r="L18" s="93"/>
+      <c r="J18" s="171"/>
+      <c r="K18" s="171"/>
+      <c r="L18" s="172"/>
     </row>
     <row r="19" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="25"/>
       <c r="B19" s="26">
         <v>3</v>
       </c>
-      <c r="C19" s="165" t="s">
+      <c r="C19" s="106" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="166"/>
-      <c r="E19" s="166"/>
-      <c r="F19" s="167"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="107"/>
+      <c r="F19" s="108"/>
       <c r="G19" s="25"/>
       <c r="H19" s="26">
         <v>2</v>
       </c>
-      <c r="I19" s="99" t="s">
+      <c r="I19" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="J19" s="100"/>
-      <c r="K19" s="100"/>
-      <c r="L19" s="101"/>
+      <c r="J19" s="86"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="92"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
       <c r="B20" s="26">
         <v>4</v>
       </c>
-      <c r="C20" s="113" t="s">
+      <c r="C20" s="102" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="114"/>
-      <c r="E20" s="114"/>
-      <c r="F20" s="115"/>
+      <c r="D20" s="87"/>
+      <c r="E20" s="87"/>
+      <c r="F20" s="88"/>
       <c r="G20" s="25"/>
       <c r="H20" s="26">
         <v>3</v>
       </c>
-      <c r="I20" s="137"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="138"/>
-      <c r="L20" s="139"/>
+      <c r="I20" s="158"/>
+      <c r="J20" s="159"/>
+      <c r="K20" s="159"/>
+      <c r="L20" s="160"/>
     </row>
     <row r="21" spans="1:12" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="25"/>
       <c r="B21" s="26">
         <v>5</v>
       </c>
-      <c r="C21" s="113" t="s">
+      <c r="C21" s="102" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="114"/>
-      <c r="E21" s="114"/>
-      <c r="F21" s="115"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="88"/>
       <c r="G21" s="25"/>
       <c r="H21" s="26">
         <v>5</v>
       </c>
-      <c r="I21" s="105" t="s">
+      <c r="I21" s="180" t="s">
         <v>26</v>
       </c>
-      <c r="J21" s="106"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="107"/>
+      <c r="J21" s="181"/>
+      <c r="K21" s="181"/>
+      <c r="L21" s="182"/>
     </row>
     <row r="22" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="29" t="s">
@@ -3045,110 +3045,110 @@
       <c r="B22" s="30">
         <v>2</v>
       </c>
-      <c r="C22" s="128"/>
-      <c r="D22" s="129"/>
-      <c r="E22" s="129"/>
-      <c r="F22" s="130"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="120"/>
       <c r="G22" s="29" t="s">
         <v>21</v>
       </c>
       <c r="H22" s="30">
         <v>2</v>
       </c>
-      <c r="I22" s="102"/>
-      <c r="J22" s="103"/>
-      <c r="K22" s="103"/>
-      <c r="L22" s="104"/>
+      <c r="I22" s="177"/>
+      <c r="J22" s="178"/>
+      <c r="K22" s="178"/>
+      <c r="L22" s="179"/>
     </row>
     <row r="23" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="25"/>
       <c r="B23" s="26">
         <v>3</v>
       </c>
-      <c r="C23" s="88" t="s">
+      <c r="C23" s="112" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="89"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="90"/>
+      <c r="D23" s="113"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="114"/>
       <c r="G23" s="25"/>
       <c r="H23" s="26">
         <v>3</v>
       </c>
-      <c r="I23" s="88" t="s">
+      <c r="I23" s="112" t="s">
         <v>95</v>
       </c>
-      <c r="J23" s="89"/>
-      <c r="K23" s="89"/>
-      <c r="L23" s="90"/>
+      <c r="J23" s="113"/>
+      <c r="K23" s="113"/>
+      <c r="L23" s="114"/>
     </row>
     <row r="24" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="49"/>
       <c r="B24" s="46">
         <v>4</v>
       </c>
-      <c r="C24" s="97" t="s">
+      <c r="C24" s="109" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="158"/>
-      <c r="E24" s="158"/>
-      <c r="F24" s="109"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="111"/>
       <c r="G24" s="49"/>
       <c r="H24" s="46">
         <v>4</v>
       </c>
-      <c r="I24" s="97" t="s">
+      <c r="I24" s="109" t="s">
         <v>102</v>
       </c>
-      <c r="J24" s="98"/>
-      <c r="K24" s="108" t="s">
+      <c r="J24" s="176"/>
+      <c r="K24" s="154" t="s">
         <v>44</v>
       </c>
-      <c r="L24" s="109"/>
+      <c r="L24" s="111"/>
     </row>
     <row r="25" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="49"/>
       <c r="B25" s="46">
         <v>5</v>
       </c>
-      <c r="C25" s="97"/>
-      <c r="D25" s="158"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="109"/>
+      <c r="C25" s="109"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="111"/>
       <c r="G25" s="49"/>
       <c r="H25" s="46">
         <v>5</v>
       </c>
-      <c r="I25" s="97" t="s">
+      <c r="I25" s="109" t="s">
         <v>40</v>
       </c>
-      <c r="J25" s="98"/>
-      <c r="K25" s="108" t="s">
+      <c r="J25" s="176"/>
+      <c r="K25" s="154" t="s">
         <v>101</v>
       </c>
-      <c r="L25" s="109"/>
+      <c r="L25" s="111"/>
     </row>
     <row r="26" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="31"/>
       <c r="B26" s="28">
         <v>6</v>
       </c>
-      <c r="C26" s="168"/>
-      <c r="D26" s="169"/>
-      <c r="E26" s="169"/>
-      <c r="F26" s="170"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="77"/>
+      <c r="E26" s="77"/>
+      <c r="F26" s="78"/>
       <c r="G26" s="31"/>
       <c r="H26" s="28">
         <v>6</v>
       </c>
-      <c r="I26" s="99" t="s">
+      <c r="I26" s="85" t="s">
         <v>162</v>
       </c>
-      <c r="J26" s="100"/>
-      <c r="K26" s="114" t="s">
+      <c r="J26" s="86"/>
+      <c r="K26" s="87" t="s">
         <v>163</v>
       </c>
-      <c r="L26" s="115"/>
+      <c r="L26" s="88"/>
     </row>
     <row r="27" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="29" t="s">
@@ -3157,86 +3157,86 @@
       <c r="B27" s="30">
         <v>2</v>
       </c>
-      <c r="C27" s="128"/>
-      <c r="D27" s="129"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="130"/>
+      <c r="C27" s="118"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="120"/>
       <c r="G27" s="29" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="30">
         <v>2</v>
       </c>
-      <c r="I27" s="174"/>
-      <c r="J27" s="175"/>
-      <c r="K27" s="175"/>
-      <c r="L27" s="176"/>
+      <c r="I27" s="82"/>
+      <c r="J27" s="83"/>
+      <c r="K27" s="83"/>
+      <c r="L27" s="84"/>
     </row>
     <row r="28" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="32"/>
       <c r="B28" s="26">
         <v>3</v>
       </c>
-      <c r="C28" s="180"/>
-      <c r="D28" s="181"/>
-      <c r="E28" s="181"/>
-      <c r="F28" s="182"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="97"/>
+      <c r="E28" s="97"/>
+      <c r="F28" s="98"/>
       <c r="G28" s="33"/>
       <c r="H28" s="26">
         <v>3</v>
       </c>
-      <c r="I28" s="140" t="s">
+      <c r="I28" s="161" t="s">
         <v>46</v>
       </c>
-      <c r="J28" s="141"/>
-      <c r="K28" s="100" t="s">
+      <c r="J28" s="162"/>
+      <c r="K28" s="86" t="s">
         <v>55</v>
       </c>
-      <c r="L28" s="101"/>
+      <c r="L28" s="92"/>
     </row>
     <row r="29" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="32"/>
       <c r="B29" s="26">
         <v>4</v>
       </c>
-      <c r="C29" s="134"/>
-      <c r="D29" s="135"/>
-      <c r="E29" s="135"/>
-      <c r="F29" s="136"/>
+      <c r="C29" s="155"/>
+      <c r="D29" s="156"/>
+      <c r="E29" s="156"/>
+      <c r="F29" s="157"/>
       <c r="G29" s="33"/>
       <c r="H29" s="26">
         <v>4</v>
       </c>
-      <c r="I29" s="99" t="s">
+      <c r="I29" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="J29" s="100"/>
-      <c r="K29" s="100" t="s">
+      <c r="J29" s="86"/>
+      <c r="K29" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="L29" s="101"/>
+      <c r="L29" s="92"/>
     </row>
     <row r="30" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="34"/>
       <c r="B30" s="28">
         <v>6</v>
       </c>
-      <c r="C30" s="177" t="s">
+      <c r="C30" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="178"/>
-      <c r="E30" s="178"/>
-      <c r="F30" s="179"/>
+      <c r="D30" s="94"/>
+      <c r="E30" s="94"/>
+      <c r="F30" s="95"/>
       <c r="G30" s="34"/>
       <c r="H30" s="28">
         <v>6</v>
       </c>
-      <c r="I30" s="76" t="s">
+      <c r="I30" s="164" t="s">
         <v>53</v>
       </c>
-      <c r="J30" s="77"/>
-      <c r="K30" s="77"/>
-      <c r="L30" s="78"/>
+      <c r="J30" s="165"/>
+      <c r="K30" s="165"/>
+      <c r="L30" s="166"/>
     </row>
     <row r="31" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="35" t="s">
@@ -3245,184 +3245,184 @@
       <c r="B31" s="30">
         <v>1</v>
       </c>
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="D31" s="80"/>
-      <c r="E31" s="80" t="s">
+      <c r="D31" s="74"/>
+      <c r="E31" s="74" t="s">
         <v>64</v>
       </c>
-      <c r="F31" s="81"/>
+      <c r="F31" s="75"/>
       <c r="G31" s="44" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="24">
         <v>1</v>
       </c>
-      <c r="I31" s="122" t="s">
+      <c r="I31" s="145" t="s">
         <v>27</v>
       </c>
-      <c r="J31" s="123"/>
-      <c r="K31" s="123"/>
-      <c r="L31" s="124"/>
+      <c r="J31" s="146"/>
+      <c r="K31" s="146"/>
+      <c r="L31" s="147"/>
     </row>
     <row r="32" spans="1:12" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="32"/>
       <c r="B32" s="26">
         <v>2</v>
       </c>
-      <c r="C32" s="85" t="s">
+      <c r="C32" s="99" t="s">
         <v>79</v>
       </c>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="87"/>
+      <c r="D32" s="100"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="101"/>
       <c r="G32" s="33"/>
       <c r="H32" s="26">
         <v>3</v>
       </c>
-      <c r="I32" s="85" t="s">
+      <c r="I32" s="99" t="s">
         <v>80</v>
       </c>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="87"/>
+      <c r="J32" s="100"/>
+      <c r="K32" s="100"/>
+      <c r="L32" s="101"/>
     </row>
     <row r="33" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="50"/>
       <c r="B33" s="26">
         <v>3</v>
       </c>
-      <c r="C33" s="85" t="s">
+      <c r="C33" s="99" t="s">
         <v>80</v>
       </c>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="87"/>
+      <c r="D33" s="100"/>
+      <c r="E33" s="100"/>
+      <c r="F33" s="101"/>
       <c r="G33" s="57"/>
       <c r="H33" s="46">
         <v>4</v>
       </c>
-      <c r="I33" s="85" t="s">
+      <c r="I33" s="99" t="s">
         <v>91</v>
       </c>
-      <c r="J33" s="86"/>
-      <c r="K33" s="86"/>
-      <c r="L33" s="87"/>
+      <c r="J33" s="100"/>
+      <c r="K33" s="100"/>
+      <c r="L33" s="101"/>
     </row>
     <row r="34" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="50"/>
       <c r="B34" s="26">
         <v>4</v>
       </c>
-      <c r="C34" s="85" t="s">
+      <c r="C34" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="87"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="101"/>
       <c r="G34" s="57"/>
       <c r="H34" s="46">
         <v>5</v>
       </c>
-      <c r="I34" s="73"/>
-      <c r="J34" s="74"/>
-      <c r="K34" s="74"/>
-      <c r="L34" s="75"/>
+      <c r="I34" s="132"/>
+      <c r="J34" s="133"/>
+      <c r="K34" s="133"/>
+      <c r="L34" s="163"/>
     </row>
     <row r="35" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="34"/>
       <c r="B35" s="28"/>
-      <c r="C35" s="131"/>
-      <c r="D35" s="132"/>
-      <c r="E35" s="132"/>
-      <c r="F35" s="133"/>
+      <c r="C35" s="151"/>
+      <c r="D35" s="152"/>
+      <c r="E35" s="152"/>
+      <c r="F35" s="153"/>
       <c r="G35" s="34"/>
       <c r="H35" s="28"/>
-      <c r="I35" s="168"/>
-      <c r="J35" s="169"/>
-      <c r="K35" s="169"/>
-      <c r="L35" s="170"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="77"/>
+      <c r="K35" s="77"/>
+      <c r="L35" s="78"/>
     </row>
     <row r="36" spans="1:12" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="36"/>
       <c r="B36" s="37"/>
-      <c r="C36" s="125"/>
-      <c r="D36" s="126"/>
-      <c r="E36" s="126"/>
-      <c r="F36" s="127"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="149"/>
+      <c r="E36" s="149"/>
+      <c r="F36" s="150"/>
       <c r="G36" s="38"/>
       <c r="H36" s="37"/>
-      <c r="I36" s="116"/>
-      <c r="J36" s="117"/>
-      <c r="K36" s="117"/>
-      <c r="L36" s="118"/>
+      <c r="I36" s="142"/>
+      <c r="J36" s="143"/>
+      <c r="K36" s="143"/>
+      <c r="L36" s="144"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37" s="39"/>
       <c r="B37" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="119" t="s">
+      <c r="C37" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="120"/>
-      <c r="E37" s="120"/>
-      <c r="F37" s="121"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="90"/>
+      <c r="F37" s="91"/>
       <c r="G37" s="39"/>
       <c r="H37" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="I37" s="119" t="s">
+      <c r="I37" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="J37" s="120"/>
-      <c r="K37" s="120"/>
-      <c r="L37" s="121"/>
+      <c r="J37" s="90"/>
+      <c r="K37" s="90"/>
+      <c r="L37" s="91"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A38" s="63"/>
       <c r="B38" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="171" t="s">
+      <c r="C38" s="79" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="172"/>
-      <c r="E38" s="172"/>
-      <c r="F38" s="173"/>
+      <c r="D38" s="80"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="81"/>
       <c r="G38" s="63"/>
       <c r="H38" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="I38" s="171" t="s">
+      <c r="I38" s="79" t="s">
         <v>92</v>
       </c>
-      <c r="J38" s="172"/>
-      <c r="K38" s="172"/>
-      <c r="L38" s="173"/>
+      <c r="J38" s="80"/>
+      <c r="K38" s="80"/>
+      <c r="L38" s="81"/>
     </row>
     <row r="39" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A39" s="48"/>
       <c r="B39" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="110" t="s">
+      <c r="C39" s="139" t="s">
         <v>71</v>
       </c>
-      <c r="D39" s="111"/>
-      <c r="E39" s="111"/>
-      <c r="F39" s="112"/>
+      <c r="D39" s="140"/>
+      <c r="E39" s="140"/>
+      <c r="F39" s="141"/>
       <c r="G39" s="48"/>
       <c r="H39" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="I39" s="110" t="s">
+      <c r="I39" s="139" t="s">
         <v>71</v>
       </c>
-      <c r="J39" s="111"/>
-      <c r="K39" s="111"/>
-      <c r="L39" s="112"/>
+      <c r="J39" s="140"/>
+      <c r="K39" s="140"/>
+      <c r="L39" s="141"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
@@ -3454,6 +3454,64 @@
     </row>
   </sheetData>
   <mergeCells count="74">
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="E16:F16"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="C26:F26"/>
@@ -3470,64 +3528,6 @@
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="I35:L35"/>
     <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="8">
@@ -3700,10 +3700,10 @@
       <c r="A7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="142" t="s">
+      <c r="C7" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="142"/>
+      <c r="D7" s="121"/>
       <c r="E7" s="15" t="s">
         <v>57</v>
       </c>
@@ -3713,10 +3713,10 @@
       <c r="G7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="142" t="s">
+      <c r="I7" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="142"/>
+      <c r="J7" s="121"/>
       <c r="K7" s="15" t="s">
         <v>58</v>
       </c>
@@ -3748,20 +3748,20 @@
       <c r="A9" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="152" t="s">
+      <c r="C9" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="152"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="152"/>
+      <c r="D9" s="131"/>
+      <c r="E9" s="131"/>
+      <c r="F9" s="131"/>
       <c r="G9" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="215" t="s">
+      <c r="I9" s="239" t="s">
         <v>89</v>
       </c>
-      <c r="J9" s="215"/>
-      <c r="K9" s="215"/>
+      <c r="J9" s="239"/>
+      <c r="K9" s="239"/>
       <c r="L9" s="42"/>
     </row>
     <row r="10" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3783,12 +3783,12 @@
       <c r="H10" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="I10" s="203" t="s">
+      <c r="I10" s="251" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="204"/>
-      <c r="K10" s="204"/>
-      <c r="L10" s="205"/>
+      <c r="J10" s="252"/>
+      <c r="K10" s="252"/>
+      <c r="L10" s="253"/>
     </row>
     <row r="11" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="23" t="s">
@@ -3797,90 +3797,90 @@
       <c r="B11" s="30">
         <v>1</v>
       </c>
-      <c r="C11" s="201" t="s">
+      <c r="C11" s="186" t="s">
         <v>109</v>
       </c>
-      <c r="D11" s="202"/>
-      <c r="E11" s="202"/>
-      <c r="F11" s="208"/>
+      <c r="D11" s="187"/>
+      <c r="E11" s="187"/>
+      <c r="F11" s="188"/>
       <c r="G11" s="23" t="s">
         <v>18</v>
       </c>
       <c r="H11" s="30">
         <v>1</v>
       </c>
-      <c r="I11" s="201" t="s">
+      <c r="I11" s="186" t="s">
         <v>110</v>
       </c>
-      <c r="J11" s="202"/>
-      <c r="K11" s="206"/>
-      <c r="L11" s="207"/>
+      <c r="J11" s="187"/>
+      <c r="K11" s="227"/>
+      <c r="L11" s="228"/>
     </row>
     <row r="12" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
       <c r="B12" s="26">
         <v>2</v>
       </c>
-      <c r="C12" s="192" t="s">
+      <c r="C12" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="193"/>
-      <c r="E12" s="193"/>
-      <c r="F12" s="194"/>
+      <c r="D12" s="217"/>
+      <c r="E12" s="217"/>
+      <c r="F12" s="218"/>
       <c r="G12" s="25"/>
       <c r="H12" s="26">
         <v>2</v>
       </c>
-      <c r="I12" s="192" t="s">
+      <c r="I12" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="J12" s="193"/>
-      <c r="K12" s="193"/>
-      <c r="L12" s="194"/>
+      <c r="J12" s="217"/>
+      <c r="K12" s="217"/>
+      <c r="L12" s="218"/>
     </row>
     <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
       <c r="B13" s="26">
         <v>3</v>
       </c>
-      <c r="C13" s="216"/>
-      <c r="D13" s="217"/>
-      <c r="E13" s="218" t="s">
+      <c r="C13" s="240"/>
+      <c r="D13" s="241"/>
+      <c r="E13" s="242" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="219"/>
+      <c r="F13" s="243"/>
       <c r="G13" s="25"/>
       <c r="H13" s="26">
         <v>3</v>
       </c>
-      <c r="I13" s="198" t="s">
+      <c r="I13" s="192" t="s">
         <v>68</v>
       </c>
-      <c r="J13" s="199"/>
-      <c r="K13" s="199"/>
-      <c r="L13" s="200"/>
+      <c r="J13" s="193"/>
+      <c r="K13" s="193"/>
+      <c r="L13" s="194"/>
     </row>
     <row r="14" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="27"/>
       <c r="B14" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="222" t="s">
+      <c r="C14" s="245" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="223"/>
-      <c r="E14" s="223"/>
-      <c r="F14" s="224"/>
+      <c r="D14" s="246"/>
+      <c r="E14" s="246"/>
+      <c r="F14" s="247"/>
       <c r="G14" s="27"/>
       <c r="H14" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="228" t="s">
+      <c r="I14" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="J14" s="229"/>
-      <c r="K14" s="229"/>
-      <c r="L14" s="230"/>
+      <c r="J14" s="190"/>
+      <c r="K14" s="190"/>
+      <c r="L14" s="191"/>
     </row>
     <row r="15" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="29" t="s">
@@ -3889,82 +3889,82 @@
       <c r="B15" s="30">
         <v>2</v>
       </c>
-      <c r="C15" s="239"/>
-      <c r="D15" s="206"/>
-      <c r="E15" s="206"/>
-      <c r="F15" s="207"/>
+      <c r="C15" s="226"/>
+      <c r="D15" s="227"/>
+      <c r="E15" s="227"/>
+      <c r="F15" s="228"/>
       <c r="G15" s="29" t="s">
         <v>19</v>
       </c>
       <c r="H15" s="30">
         <v>2</v>
       </c>
-      <c r="I15" s="245"/>
-      <c r="J15" s="246"/>
-      <c r="K15" s="246"/>
-      <c r="L15" s="247"/>
+      <c r="I15" s="183"/>
+      <c r="J15" s="184"/>
+      <c r="K15" s="184"/>
+      <c r="L15" s="185"/>
     </row>
     <row r="16" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
         <v>3</v>
       </c>
-      <c r="C16" s="189"/>
-      <c r="D16" s="190"/>
-      <c r="E16" s="190"/>
-      <c r="F16" s="191"/>
+      <c r="C16" s="256"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="257"/>
+      <c r="F16" s="258"/>
       <c r="G16" s="25"/>
       <c r="H16" s="26">
         <v>3</v>
       </c>
-      <c r="I16" s="192" t="s">
+      <c r="I16" s="216" t="s">
         <v>116</v>
       </c>
-      <c r="J16" s="193"/>
-      <c r="K16" s="193"/>
-      <c r="L16" s="194"/>
+      <c r="J16" s="217"/>
+      <c r="K16" s="217"/>
+      <c r="L16" s="218"/>
     </row>
     <row r="17" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="25"/>
       <c r="B17" s="26">
         <v>4</v>
       </c>
-      <c r="C17" s="192" t="s">
+      <c r="C17" s="216" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="193"/>
-      <c r="E17" s="193"/>
-      <c r="F17" s="194"/>
+      <c r="D17" s="217"/>
+      <c r="E17" s="217"/>
+      <c r="F17" s="218"/>
       <c r="G17" s="25"/>
       <c r="H17" s="26">
         <v>4</v>
       </c>
-      <c r="I17" s="192" t="s">
+      <c r="I17" s="216" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="193"/>
-      <c r="K17" s="193"/>
-      <c r="L17" s="194"/>
+      <c r="J17" s="217"/>
+      <c r="K17" s="217"/>
+      <c r="L17" s="218"/>
     </row>
     <row r="18" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="31"/>
       <c r="B18" s="28">
         <v>5</v>
       </c>
-      <c r="C18" s="195" t="s">
+      <c r="C18" s="259" t="s">
         <v>116</v>
       </c>
-      <c r="D18" s="196"/>
-      <c r="E18" s="196"/>
-      <c r="F18" s="197"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="261"/>
       <c r="G18" s="31"/>
       <c r="H18" s="28">
         <v>5</v>
       </c>
-      <c r="I18" s="231"/>
-      <c r="J18" s="232"/>
-      <c r="K18" s="232"/>
-      <c r="L18" s="233"/>
+      <c r="I18" s="219"/>
+      <c r="J18" s="220"/>
+      <c r="K18" s="220"/>
+      <c r="L18" s="221"/>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="29" t="s">
@@ -3973,94 +3973,94 @@
       <c r="B19" s="30">
         <v>1</v>
       </c>
-      <c r="C19" s="201" t="s">
+      <c r="C19" s="186" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="202"/>
-      <c r="E19" s="202"/>
-      <c r="F19" s="208"/>
+      <c r="D19" s="187"/>
+      <c r="E19" s="187"/>
+      <c r="F19" s="188"/>
       <c r="G19" s="29" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="30">
         <v>1</v>
       </c>
-      <c r="I19" s="201" t="s">
+      <c r="I19" s="186" t="s">
         <v>106</v>
       </c>
-      <c r="J19" s="202"/>
-      <c r="K19" s="202"/>
-      <c r="L19" s="208"/>
+      <c r="J19" s="187"/>
+      <c r="K19" s="187"/>
+      <c r="L19" s="188"/>
     </row>
     <row r="20" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
       <c r="B20" s="26">
         <v>2</v>
       </c>
-      <c r="C20" s="198" t="s">
+      <c r="C20" s="192" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="199"/>
-      <c r="E20" s="199"/>
-      <c r="F20" s="200"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="193"/>
+      <c r="F20" s="194"/>
       <c r="G20" s="25"/>
       <c r="H20" s="26">
         <v>2</v>
       </c>
-      <c r="I20" s="198" t="s">
+      <c r="I20" s="192" t="s">
         <v>111</v>
       </c>
-      <c r="J20" s="199"/>
-      <c r="K20" s="199"/>
-      <c r="L20" s="200"/>
+      <c r="J20" s="193"/>
+      <c r="K20" s="193"/>
+      <c r="L20" s="194"/>
     </row>
     <row r="21" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="25"/>
       <c r="B21" s="26">
         <v>3</v>
       </c>
-      <c r="C21" s="183" t="s">
+      <c r="C21" s="231" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="184"/>
-      <c r="E21" s="185" t="s">
+      <c r="D21" s="232"/>
+      <c r="E21" s="229" t="s">
         <v>108</v>
       </c>
-      <c r="F21" s="186"/>
+      <c r="F21" s="230"/>
       <c r="G21" s="25"/>
       <c r="H21" s="26">
         <v>3</v>
       </c>
-      <c r="I21" s="187" t="s">
+      <c r="I21" s="254" t="s">
         <v>49</v>
       </c>
-      <c r="J21" s="188"/>
-      <c r="K21" s="185" t="s">
+      <c r="J21" s="255"/>
+      <c r="K21" s="229" t="s">
         <v>105</v>
       </c>
-      <c r="L21" s="186"/>
+      <c r="L21" s="230"/>
     </row>
     <row r="22" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="25"/>
       <c r="B22" s="26">
         <v>4</v>
       </c>
-      <c r="C22" s="244" t="s">
+      <c r="C22" s="195" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="237"/>
-      <c r="E22" s="237" t="s">
+      <c r="D22" s="196"/>
+      <c r="E22" s="196" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="238"/>
+      <c r="F22" s="225"/>
       <c r="G22" s="25"/>
       <c r="H22" s="26">
         <v>4</v>
       </c>
-      <c r="I22" s="241"/>
-      <c r="J22" s="242"/>
-      <c r="K22" s="242"/>
-      <c r="L22" s="243"/>
+      <c r="I22" s="233"/>
+      <c r="J22" s="234"/>
+      <c r="K22" s="234"/>
+      <c r="L22" s="235"/>
     </row>
     <row r="23" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="29" t="s">
@@ -4069,92 +4069,92 @@
       <c r="B23" s="30">
         <v>1</v>
       </c>
-      <c r="C23" s="225" t="s">
+      <c r="C23" s="248" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="226"/>
-      <c r="E23" s="226"/>
-      <c r="F23" s="227"/>
+      <c r="D23" s="249"/>
+      <c r="E23" s="249"/>
+      <c r="F23" s="250"/>
       <c r="G23" s="29" t="s">
         <v>21</v>
       </c>
       <c r="H23" s="30">
         <v>1</v>
       </c>
-      <c r="I23" s="201" t="s">
+      <c r="I23" s="186" t="s">
         <v>51</v>
       </c>
-      <c r="J23" s="202"/>
-      <c r="K23" s="202"/>
-      <c r="L23" s="208"/>
+      <c r="J23" s="187"/>
+      <c r="K23" s="187"/>
+      <c r="L23" s="188"/>
     </row>
     <row r="24" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="25"/>
       <c r="B24" s="26">
         <v>2</v>
       </c>
-      <c r="C24" s="183" t="s">
+      <c r="C24" s="231" t="s">
         <v>113</v>
       </c>
-      <c r="D24" s="184"/>
-      <c r="E24" s="185"/>
-      <c r="F24" s="186"/>
+      <c r="D24" s="232"/>
+      <c r="E24" s="229"/>
+      <c r="F24" s="230"/>
       <c r="G24" s="25"/>
       <c r="H24" s="26">
         <v>2</v>
       </c>
-      <c r="I24" s="198" t="s">
+      <c r="I24" s="192" t="s">
         <v>48</v>
       </c>
-      <c r="J24" s="199"/>
-      <c r="K24" s="199" t="s">
+      <c r="J24" s="193"/>
+      <c r="K24" s="193" t="s">
         <v>45</v>
       </c>
-      <c r="L24" s="200"/>
+      <c r="L24" s="194"/>
     </row>
     <row r="25" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="25"/>
       <c r="B25" s="26">
         <v>3</v>
       </c>
-      <c r="C25" s="198" t="s">
+      <c r="C25" s="192" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="199"/>
-      <c r="E25" s="220"/>
-      <c r="F25" s="221"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="198"/>
+      <c r="F25" s="244"/>
       <c r="G25" s="25"/>
       <c r="H25" s="26">
         <v>3</v>
       </c>
-      <c r="I25" s="240"/>
-      <c r="J25" s="220"/>
-      <c r="K25" s="199" t="s">
+      <c r="I25" s="197"/>
+      <c r="J25" s="198"/>
+      <c r="K25" s="193" t="s">
         <v>114</v>
       </c>
-      <c r="L25" s="200"/>
+      <c r="L25" s="194"/>
     </row>
     <row r="26" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="31"/>
       <c r="B26" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="234" t="s">
+      <c r="C26" s="222" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="235"/>
-      <c r="E26" s="235"/>
-      <c r="F26" s="236"/>
+      <c r="D26" s="223"/>
+      <c r="E26" s="223"/>
+      <c r="F26" s="224"/>
       <c r="G26" s="31"/>
       <c r="H26" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="I26" s="228" t="s">
+      <c r="I26" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="J26" s="229"/>
-      <c r="K26" s="229"/>
-      <c r="L26" s="230"/>
+      <c r="J26" s="190"/>
+      <c r="K26" s="190"/>
+      <c r="L26" s="191"/>
     </row>
     <row r="27" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="29" t="s">
@@ -4163,88 +4163,88 @@
       <c r="B27" s="30">
         <v>2</v>
       </c>
-      <c r="C27" s="201" t="s">
+      <c r="C27" s="186" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="202"/>
-      <c r="E27" s="202"/>
-      <c r="F27" s="208"/>
+      <c r="D27" s="187"/>
+      <c r="E27" s="187"/>
+      <c r="F27" s="188"/>
       <c r="G27" s="29" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="30">
         <v>2</v>
       </c>
-      <c r="I27" s="245"/>
-      <c r="J27" s="246"/>
-      <c r="K27" s="246"/>
-      <c r="L27" s="247"/>
+      <c r="I27" s="183"/>
+      <c r="J27" s="184"/>
+      <c r="K27" s="184"/>
+      <c r="L27" s="185"/>
     </row>
     <row r="28" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="32"/>
       <c r="B28" s="24">
         <v>3</v>
       </c>
-      <c r="C28" s="192" t="s">
+      <c r="C28" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="193"/>
-      <c r="E28" s="193"/>
-      <c r="F28" s="194"/>
+      <c r="D28" s="217"/>
+      <c r="E28" s="217"/>
+      <c r="F28" s="218"/>
       <c r="G28" s="32"/>
       <c r="H28" s="24">
         <v>3</v>
       </c>
-      <c r="I28" s="192" t="s">
+      <c r="I28" s="216" t="s">
         <v>67</v>
       </c>
-      <c r="J28" s="193"/>
-      <c r="K28" s="193"/>
-      <c r="L28" s="194"/>
+      <c r="J28" s="217"/>
+      <c r="K28" s="217"/>
+      <c r="L28" s="218"/>
     </row>
     <row r="29" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="32"/>
       <c r="B29" s="26">
         <v>4</v>
       </c>
-      <c r="C29" s="240"/>
-      <c r="D29" s="220"/>
-      <c r="E29" s="199" t="s">
+      <c r="C29" s="197"/>
+      <c r="D29" s="198"/>
+      <c r="E29" s="193" t="s">
         <v>115</v>
       </c>
-      <c r="F29" s="200"/>
+      <c r="F29" s="194"/>
       <c r="G29" s="32"/>
       <c r="H29" s="26">
         <v>4</v>
       </c>
-      <c r="I29" s="198" t="s">
+      <c r="I29" s="192" t="s">
         <v>68</v>
       </c>
-      <c r="J29" s="199"/>
-      <c r="K29" s="199"/>
-      <c r="L29" s="200"/>
+      <c r="J29" s="193"/>
+      <c r="K29" s="193"/>
+      <c r="L29" s="194"/>
     </row>
     <row r="30" spans="1:12" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="32"/>
       <c r="B30" s="26">
         <v>5</v>
       </c>
-      <c r="C30" s="212"/>
-      <c r="D30" s="213"/>
-      <c r="E30" s="213"/>
-      <c r="F30" s="214"/>
+      <c r="C30" s="236"/>
+      <c r="D30" s="237"/>
+      <c r="E30" s="237"/>
+      <c r="F30" s="238"/>
       <c r="G30" s="32"/>
       <c r="H30" s="26">
         <v>5</v>
       </c>
-      <c r="I30" s="250" t="s">
+      <c r="I30" s="201" t="s">
         <v>107</v>
       </c>
-      <c r="J30" s="251"/>
-      <c r="K30" s="251" t="s">
+      <c r="J30" s="202"/>
+      <c r="K30" s="202" t="s">
         <v>47</v>
       </c>
-      <c r="L30" s="252"/>
+      <c r="L30" s="203"/>
     </row>
     <row r="31" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="35" t="s">
@@ -4253,122 +4253,122 @@
       <c r="B31" s="30">
         <v>2</v>
       </c>
-      <c r="C31" s="209" t="s">
+      <c r="C31" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="210"/>
-      <c r="E31" s="210"/>
-      <c r="F31" s="211"/>
+      <c r="D31" s="214"/>
+      <c r="E31" s="214"/>
+      <c r="F31" s="215"/>
       <c r="G31" s="35" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="30">
         <v>2</v>
       </c>
-      <c r="I31" s="209" t="s">
+      <c r="I31" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="J31" s="210"/>
-      <c r="K31" s="210"/>
-      <c r="L31" s="211"/>
+      <c r="J31" s="214"/>
+      <c r="K31" s="214"/>
+      <c r="L31" s="215"/>
     </row>
     <row r="32" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="41"/>
       <c r="B32" s="26">
         <v>3</v>
       </c>
-      <c r="C32" s="256"/>
-      <c r="D32" s="257"/>
-      <c r="E32" s="257"/>
-      <c r="F32" s="258"/>
+      <c r="C32" s="207"/>
+      <c r="D32" s="208"/>
+      <c r="E32" s="208"/>
+      <c r="F32" s="209"/>
       <c r="G32" s="41"/>
       <c r="H32" s="26">
         <v>3</v>
       </c>
-      <c r="I32" s="256"/>
-      <c r="J32" s="257"/>
-      <c r="K32" s="257"/>
-      <c r="L32" s="258"/>
+      <c r="I32" s="207"/>
+      <c r="J32" s="208"/>
+      <c r="K32" s="208"/>
+      <c r="L32" s="209"/>
     </row>
     <row r="33" spans="1:12" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="45"/>
       <c r="B33" s="46"/>
-      <c r="C33" s="253"/>
-      <c r="D33" s="254"/>
-      <c r="E33" s="254"/>
-      <c r="F33" s="255"/>
+      <c r="C33" s="204"/>
+      <c r="D33" s="205"/>
+      <c r="E33" s="205"/>
+      <c r="F33" s="206"/>
       <c r="G33" s="48"/>
       <c r="H33" s="28"/>
-      <c r="I33" s="259"/>
-      <c r="J33" s="260"/>
-      <c r="K33" s="260"/>
-      <c r="L33" s="261"/>
+      <c r="I33" s="210"/>
+      <c r="J33" s="211"/>
+      <c r="K33" s="211"/>
+      <c r="L33" s="212"/>
     </row>
     <row r="34" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="39"/>
       <c r="B34" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="201" t="s">
+      <c r="C34" s="186" t="s">
         <v>104</v>
       </c>
-      <c r="D34" s="202"/>
-      <c r="E34" s="202"/>
-      <c r="F34" s="208"/>
+      <c r="D34" s="187"/>
+      <c r="E34" s="187"/>
+      <c r="F34" s="188"/>
       <c r="G34" s="39"/>
       <c r="H34" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="201" t="s">
+      <c r="I34" s="186" t="s">
         <v>104</v>
       </c>
-      <c r="J34" s="202"/>
-      <c r="K34" s="202"/>
-      <c r="L34" s="208"/>
+      <c r="J34" s="187"/>
+      <c r="K34" s="187"/>
+      <c r="L34" s="188"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="48"/>
       <c r="B35" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="250" t="s">
+      <c r="C35" s="201" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="251"/>
-      <c r="E35" s="251"/>
-      <c r="F35" s="252"/>
+      <c r="D35" s="202"/>
+      <c r="E35" s="202"/>
+      <c r="F35" s="203"/>
       <c r="G35" s="48"/>
       <c r="H35" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="I35" s="250" t="s">
+      <c r="I35" s="201" t="s">
         <v>103</v>
       </c>
-      <c r="J35" s="251"/>
-      <c r="K35" s="251"/>
-      <c r="L35" s="252"/>
+      <c r="J35" s="202"/>
+      <c r="K35" s="202"/>
+      <c r="L35" s="203"/>
     </row>
     <row r="36" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="51" t="s">
         <v>62</v>
       </c>
       <c r="B36" s="52"/>
-      <c r="C36" s="248" t="s">
+      <c r="C36" s="199" t="s">
         <v>73</v>
       </c>
-      <c r="D36" s="248"/>
-      <c r="E36" s="248"/>
-      <c r="F36" s="248"/>
+      <c r="D36" s="199"/>
+      <c r="E36" s="199"/>
+      <c r="F36" s="199"/>
       <c r="G36" s="51" t="s">
         <v>62</v>
       </c>
       <c r="H36" s="52"/>
-      <c r="I36" s="249" t="s">
+      <c r="I36" s="200" t="s">
         <v>73</v>
       </c>
-      <c r="J36" s="249"/>
-      <c r="K36" s="249"/>
-      <c r="L36" s="249"/>
+      <c r="J36" s="200"/>
+      <c r="K36" s="200"/>
+      <c r="L36" s="200"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37" s="2" t="s">
@@ -4400,12 +4400,52 @@
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="I22:L22"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="I27:L27"/>
     <mergeCell ref="I25:J25"/>
@@ -4422,52 +4462,12 @@
     <mergeCell ref="I32:L32"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C34:F34"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="K24:L24"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:E8">
     <cfRule type="expression" priority="8">
@@ -4657,10 +4657,10 @@
       <c r="A7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="142" t="s">
+      <c r="C7" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="142"/>
+      <c r="D7" s="121"/>
       <c r="E7" s="15" t="s">
         <v>42</v>
       </c>
@@ -4670,10 +4670,10 @@
       <c r="G7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="142" t="s">
+      <c r="I7" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="142"/>
+      <c r="J7" s="121"/>
       <c r="K7" s="15" t="s">
         <v>43</v>
       </c>
@@ -4705,20 +4705,20 @@
       <c r="A9" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="152" t="s">
+      <c r="C9" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="152"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="152"/>
+      <c r="D9" s="131"/>
+      <c r="E9" s="131"/>
+      <c r="F9" s="131"/>
       <c r="G9" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="215" t="s">
+      <c r="I9" s="239" t="s">
         <v>89</v>
       </c>
-      <c r="J9" s="215"/>
-      <c r="K9" s="215"/>
+      <c r="J9" s="239"/>
+      <c r="K9" s="239"/>
       <c r="L9" s="42"/>
     </row>
     <row r="10" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4764,12 +4764,12 @@
       <c r="H11" s="24">
         <v>2</v>
       </c>
-      <c r="I11" s="79" t="s">
+      <c r="I11" s="73" t="s">
         <v>123</v>
       </c>
-      <c r="J11" s="80"/>
-      <c r="K11" s="80"/>
-      <c r="L11" s="81"/>
+      <c r="J11" s="74"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="75"/>
     </row>
     <row r="12" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
@@ -4786,34 +4786,34 @@
       <c r="H12" s="26">
         <v>3</v>
       </c>
-      <c r="I12" s="99" t="s">
+      <c r="I12" s="85" t="s">
         <v>78</v>
       </c>
-      <c r="J12" s="100"/>
-      <c r="K12" s="100"/>
-      <c r="L12" s="101"/>
+      <c r="J12" s="86"/>
+      <c r="K12" s="86"/>
+      <c r="L12" s="92"/>
     </row>
     <row r="13" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
       <c r="B13" s="26">
         <v>4</v>
       </c>
-      <c r="C13" s="99" t="s">
+      <c r="C13" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="100"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="101"/>
+      <c r="D13" s="86"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="92"/>
       <c r="G13" s="25"/>
       <c r="H13" s="26">
         <v>4</v>
       </c>
-      <c r="I13" s="99" t="s">
+      <c r="I13" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="100"/>
-      <c r="K13" s="100"/>
-      <c r="L13" s="101"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="92"/>
     </row>
     <row r="14" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="27"/>
@@ -4828,12 +4828,12 @@
       <c r="H14" s="28">
         <v>5</v>
       </c>
-      <c r="I14" s="268" t="s">
+      <c r="I14" s="296" t="s">
         <v>126</v>
       </c>
-      <c r="J14" s="269"/>
-      <c r="K14" s="269"/>
-      <c r="L14" s="270"/>
+      <c r="J14" s="297"/>
+      <c r="K14" s="297"/>
+      <c r="L14" s="298"/>
     </row>
     <row r="15" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="29" t="s">
@@ -4852,72 +4852,72 @@
       <c r="H15" s="30">
         <v>2</v>
       </c>
-      <c r="I15" s="271"/>
-      <c r="J15" s="272"/>
-      <c r="K15" s="272"/>
-      <c r="L15" s="273"/>
+      <c r="I15" s="299"/>
+      <c r="J15" s="300"/>
+      <c r="K15" s="300"/>
+      <c r="L15" s="301"/>
     </row>
     <row r="16" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
         <v>4</v>
       </c>
-      <c r="C16" s="165" t="s">
+      <c r="C16" s="106" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="292"/>
-      <c r="E16" s="262"/>
-      <c r="F16" s="182"/>
+      <c r="D16" s="295"/>
+      <c r="E16" s="305"/>
+      <c r="F16" s="98"/>
       <c r="G16" s="25"/>
       <c r="H16" s="26">
         <v>3</v>
       </c>
-      <c r="I16" s="155"/>
-      <c r="J16" s="156"/>
-      <c r="K16" s="156"/>
-      <c r="L16" s="157"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="137"/>
+      <c r="K16" s="137"/>
+      <c r="L16" s="138"/>
     </row>
     <row r="17" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="25"/>
       <c r="B17" s="26">
         <v>5</v>
       </c>
-      <c r="C17" s="137"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="139"/>
+      <c r="C17" s="158"/>
+      <c r="D17" s="159"/>
+      <c r="E17" s="159"/>
+      <c r="F17" s="160"/>
       <c r="G17" s="25"/>
       <c r="H17" s="26">
         <v>4</v>
       </c>
-      <c r="I17" s="99" t="s">
+      <c r="I17" s="85" t="s">
         <v>127</v>
       </c>
-      <c r="J17" s="100"/>
-      <c r="K17" s="100"/>
-      <c r="L17" s="101"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
+      <c r="L17" s="92"/>
     </row>
     <row r="18" spans="1:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="31"/>
       <c r="B18" s="28">
         <v>6</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="164" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="78"/>
+      <c r="D18" s="165"/>
+      <c r="E18" s="165"/>
+      <c r="F18" s="166"/>
       <c r="G18" s="31"/>
       <c r="H18" s="28">
         <v>5</v>
       </c>
-      <c r="I18" s="76" t="s">
+      <c r="I18" s="164" t="s">
         <v>125</v>
       </c>
-      <c r="J18" s="77"/>
-      <c r="K18" s="77"/>
-      <c r="L18" s="78"/>
+      <c r="J18" s="165"/>
+      <c r="K18" s="165"/>
+      <c r="L18" s="166"/>
     </row>
     <row r="19" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="29" t="s">
@@ -4926,88 +4926,88 @@
       <c r="B19" s="30">
         <v>2</v>
       </c>
-      <c r="C19" s="277" t="s">
+      <c r="C19" s="292" t="s">
         <v>129</v>
       </c>
-      <c r="D19" s="278"/>
-      <c r="E19" s="278"/>
-      <c r="F19" s="279"/>
+      <c r="D19" s="293"/>
+      <c r="E19" s="293"/>
+      <c r="F19" s="294"/>
       <c r="G19" s="29" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="30">
         <v>2</v>
       </c>
-      <c r="I19" s="277" t="s">
+      <c r="I19" s="292" t="s">
         <v>128</v>
       </c>
-      <c r="J19" s="278"/>
-      <c r="K19" s="278"/>
-      <c r="L19" s="279"/>
+      <c r="J19" s="293"/>
+      <c r="K19" s="293"/>
+      <c r="L19" s="294"/>
     </row>
     <row r="20" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
       <c r="B20" s="26">
         <v>3</v>
       </c>
-      <c r="C20" s="99" t="s">
+      <c r="C20" s="85" t="s">
         <v>130</v>
       </c>
-      <c r="D20" s="100"/>
-      <c r="E20" s="100"/>
-      <c r="F20" s="101"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="92"/>
       <c r="G20" s="25"/>
       <c r="H20" s="26">
         <v>3</v>
       </c>
-      <c r="I20" s="99" t="s">
+      <c r="I20" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="J20" s="100"/>
-      <c r="K20" s="100"/>
-      <c r="L20" s="101"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="92"/>
     </row>
     <row r="21" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="25"/>
       <c r="B21" s="26">
         <v>4</v>
       </c>
-      <c r="C21" s="99" t="s">
+      <c r="C21" s="85" t="s">
         <v>131</v>
       </c>
-      <c r="D21" s="100"/>
-      <c r="E21" s="100"/>
-      <c r="F21" s="101"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="92"/>
       <c r="G21" s="25"/>
       <c r="H21" s="26">
         <v>4</v>
       </c>
-      <c r="I21" s="99" t="s">
+      <c r="I21" s="85" t="s">
         <v>131</v>
       </c>
-      <c r="J21" s="100"/>
-      <c r="K21" s="100"/>
-      <c r="L21" s="101"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="86"/>
+      <c r="L21" s="92"/>
     </row>
     <row r="22" spans="1:13" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="31"/>
       <c r="B22" s="28">
         <v>5</v>
       </c>
-      <c r="C22" s="177" t="s">
+      <c r="C22" s="93" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="178"/>
-      <c r="E22" s="178"/>
-      <c r="F22" s="179"/>
+      <c r="D22" s="94"/>
+      <c r="E22" s="94"/>
+      <c r="F22" s="95"/>
       <c r="G22" s="31"/>
       <c r="H22" s="28">
         <v>5</v>
       </c>
-      <c r="I22" s="143"/>
-      <c r="J22" s="144"/>
-      <c r="K22" s="144"/>
-      <c r="L22" s="145"/>
+      <c r="I22" s="122"/>
+      <c r="J22" s="123"/>
+      <c r="K22" s="123"/>
+      <c r="L22" s="124"/>
     </row>
     <row r="23" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="29" t="s">
@@ -5016,90 +5016,90 @@
       <c r="B23" s="30">
         <v>2</v>
       </c>
-      <c r="C23" s="263" t="s">
+      <c r="C23" s="277" t="s">
         <v>133</v>
       </c>
-      <c r="D23" s="264"/>
-      <c r="E23" s="264" t="s">
+      <c r="D23" s="278"/>
+      <c r="E23" s="278" t="s">
         <v>134</v>
       </c>
-      <c r="F23" s="265"/>
+      <c r="F23" s="279"/>
       <c r="G23" s="29" t="s">
         <v>21</v>
       </c>
       <c r="H23" s="24">
         <v>2</v>
       </c>
-      <c r="I23" s="274"/>
-      <c r="J23" s="275"/>
-      <c r="K23" s="275"/>
-      <c r="L23" s="276"/>
+      <c r="I23" s="302"/>
+      <c r="J23" s="303"/>
+      <c r="K23" s="303"/>
+      <c r="L23" s="304"/>
     </row>
     <row r="24" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="25"/>
       <c r="B24" s="24">
         <v>3</v>
       </c>
-      <c r="C24" s="99" t="s">
+      <c r="C24" s="85" t="s">
         <v>135</v>
       </c>
-      <c r="D24" s="100"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="101"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="92"/>
       <c r="G24" s="25"/>
       <c r="H24" s="24">
         <v>3</v>
       </c>
-      <c r="I24" s="73" t="s">
+      <c r="I24" s="132" t="s">
         <v>135</v>
       </c>
-      <c r="J24" s="74"/>
-      <c r="K24" s="74"/>
-      <c r="L24" s="75"/>
+      <c r="J24" s="133"/>
+      <c r="K24" s="133"/>
+      <c r="L24" s="163"/>
     </row>
     <row r="25" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="25"/>
       <c r="B25" s="24">
         <v>4</v>
       </c>
-      <c r="C25" s="99" t="s">
+      <c r="C25" s="85" t="s">
         <v>158</v>
       </c>
-      <c r="D25" s="100"/>
-      <c r="E25" s="100" t="s">
+      <c r="D25" s="86"/>
+      <c r="E25" s="86" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="101"/>
+      <c r="F25" s="92"/>
       <c r="G25" s="25"/>
       <c r="H25" s="24">
         <v>4</v>
       </c>
-      <c r="I25" s="97" t="s">
+      <c r="I25" s="109" t="s">
         <v>136</v>
       </c>
-      <c r="J25" s="158"/>
-      <c r="K25" s="158"/>
-      <c r="L25" s="109"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="110"/>
+      <c r="L25" s="111"/>
     </row>
     <row r="26" spans="1:13" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="25"/>
       <c r="B26" s="26">
         <v>5</v>
       </c>
-      <c r="C26" s="266"/>
-      <c r="D26" s="267"/>
-      <c r="E26" s="95" t="s">
+      <c r="C26" s="306"/>
+      <c r="D26" s="307"/>
+      <c r="E26" s="174" t="s">
         <v>159</v>
       </c>
-      <c r="F26" s="96"/>
+      <c r="F26" s="175"/>
       <c r="G26" s="25"/>
       <c r="H26" s="26">
         <v>5</v>
       </c>
-      <c r="I26" s="155"/>
-      <c r="J26" s="156"/>
-      <c r="K26" s="156"/>
-      <c r="L26" s="157"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="137"/>
+      <c r="K26" s="137"/>
+      <c r="L26" s="138"/>
     </row>
     <row r="27" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="29" t="s">
@@ -5108,66 +5108,66 @@
       <c r="B27" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="162" t="s">
+      <c r="C27" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="163"/>
-      <c r="E27" s="163"/>
-      <c r="F27" s="164"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="105"/>
       <c r="G27" s="29" t="s">
         <v>22</v>
       </c>
       <c r="H27" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="I27" s="293" t="s">
+      <c r="I27" s="262" t="s">
         <v>61</v>
       </c>
-      <c r="J27" s="294"/>
-      <c r="K27" s="294"/>
-      <c r="L27" s="295"/>
+      <c r="J27" s="263"/>
+      <c r="K27" s="263"/>
+      <c r="L27" s="264"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="32"/>
       <c r="B28" s="24">
         <v>4</v>
       </c>
-      <c r="C28" s="99" t="s">
+      <c r="C28" s="85" t="s">
         <v>160</v>
       </c>
-      <c r="D28" s="100"/>
-      <c r="E28" s="100"/>
-      <c r="F28" s="101"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="92"/>
       <c r="G28" s="32"/>
       <c r="H28" s="24">
         <v>4</v>
       </c>
-      <c r="I28" s="99" t="s">
+      <c r="I28" s="85" t="s">
         <v>137</v>
       </c>
-      <c r="J28" s="100"/>
-      <c r="K28" s="100"/>
-      <c r="L28" s="101"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="92"/>
     </row>
     <row r="29" spans="1:13" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="32"/>
       <c r="B29" s="26">
         <v>5</v>
       </c>
-      <c r="C29" s="305"/>
-      <c r="D29" s="306"/>
-      <c r="E29" s="306"/>
-      <c r="F29" s="307"/>
+      <c r="C29" s="274"/>
+      <c r="D29" s="275"/>
+      <c r="E29" s="275"/>
+      <c r="F29" s="276"/>
       <c r="G29" s="32"/>
       <c r="H29" s="26">
         <v>5</v>
       </c>
-      <c r="I29" s="73" t="s">
+      <c r="I29" s="132" t="s">
         <v>138</v>
       </c>
-      <c r="J29" s="74"/>
-      <c r="K29" s="74"/>
-      <c r="L29" s="75"/>
+      <c r="J29" s="133"/>
+      <c r="K29" s="133"/>
+      <c r="L29" s="163"/>
       <c r="M29" s="47"/>
     </row>
     <row r="30" spans="1:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -5177,84 +5177,84 @@
       <c r="B30" s="30">
         <v>1</v>
       </c>
-      <c r="C30" s="263" t="s">
+      <c r="C30" s="277" t="s">
         <v>119</v>
       </c>
-      <c r="D30" s="264"/>
-      <c r="E30" s="264"/>
-      <c r="F30" s="265"/>
+      <c r="D30" s="278"/>
+      <c r="E30" s="278"/>
+      <c r="F30" s="279"/>
       <c r="G30" s="35" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="30">
         <v>1</v>
       </c>
-      <c r="I30" s="263" t="s">
+      <c r="I30" s="277" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="264"/>
-      <c r="K30" s="264"/>
-      <c r="L30" s="265"/>
+      <c r="J30" s="278"/>
+      <c r="K30" s="278"/>
+      <c r="L30" s="279"/>
     </row>
     <row r="31" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="41"/>
       <c r="B31" s="24">
         <v>2</v>
       </c>
-      <c r="C31" s="99" t="s">
+      <c r="C31" s="85" t="s">
         <v>120</v>
       </c>
-      <c r="D31" s="100"/>
-      <c r="E31" s="100" t="s">
+      <c r="D31" s="86"/>
+      <c r="E31" s="86" t="s">
         <v>121</v>
       </c>
-      <c r="F31" s="101"/>
+      <c r="F31" s="92"/>
       <c r="G31" s="41"/>
       <c r="H31" s="24">
         <v>2</v>
       </c>
-      <c r="I31" s="155"/>
-      <c r="J31" s="156"/>
-      <c r="K31" s="156"/>
-      <c r="L31" s="157"/>
+      <c r="I31" s="136"/>
+      <c r="J31" s="137"/>
+      <c r="K31" s="137"/>
+      <c r="L31" s="138"/>
     </row>
     <row r="32" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="45"/>
       <c r="B32" s="58">
         <v>3</v>
       </c>
-      <c r="C32" s="113"/>
-      <c r="D32" s="114"/>
-      <c r="E32" s="114" t="s">
+      <c r="C32" s="102"/>
+      <c r="D32" s="87"/>
+      <c r="E32" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="F32" s="115"/>
+      <c r="F32" s="88"/>
       <c r="G32" s="45"/>
       <c r="H32" s="58">
         <v>3</v>
       </c>
-      <c r="I32" s="155"/>
-      <c r="J32" s="156"/>
-      <c r="K32" s="156"/>
-      <c r="L32" s="157"/>
+      <c r="I32" s="136"/>
+      <c r="J32" s="137"/>
+      <c r="K32" s="137"/>
+      <c r="L32" s="138"/>
     </row>
     <row r="33" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="48"/>
       <c r="B33" s="28">
         <v>4</v>
       </c>
-      <c r="C33" s="299"/>
-      <c r="D33" s="300"/>
-      <c r="E33" s="300"/>
-      <c r="F33" s="301"/>
+      <c r="C33" s="268"/>
+      <c r="D33" s="269"/>
+      <c r="E33" s="269"/>
+      <c r="F33" s="270"/>
       <c r="G33" s="48"/>
       <c r="H33" s="28">
         <v>4</v>
       </c>
-      <c r="I33" s="302"/>
-      <c r="J33" s="303"/>
-      <c r="K33" s="303"/>
-      <c r="L33" s="304"/>
+      <c r="I33" s="271"/>
+      <c r="J33" s="272"/>
+      <c r="K33" s="272"/>
+      <c r="L33" s="273"/>
     </row>
     <row r="34" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="38"/>
@@ -5275,66 +5275,66 @@
       <c r="B35" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="293" t="s">
+      <c r="C35" s="262" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="294"/>
-      <c r="E35" s="294"/>
-      <c r="F35" s="295"/>
+      <c r="D35" s="263"/>
+      <c r="E35" s="263"/>
+      <c r="F35" s="264"/>
       <c r="G35" s="65"/>
       <c r="H35" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="I35" s="293" t="s">
+      <c r="I35" s="262" t="s">
         <v>117</v>
       </c>
-      <c r="J35" s="294"/>
-      <c r="K35" s="294"/>
-      <c r="L35" s="295"/>
+      <c r="J35" s="263"/>
+      <c r="K35" s="263"/>
+      <c r="L35" s="264"/>
     </row>
     <row r="36" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="66"/>
       <c r="B36" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="296" t="s">
+      <c r="C36" s="265" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="297"/>
-      <c r="E36" s="297"/>
-      <c r="F36" s="298"/>
+      <c r="D36" s="266"/>
+      <c r="E36" s="266"/>
+      <c r="F36" s="267"/>
       <c r="G36" s="66"/>
       <c r="H36" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="296" t="s">
+      <c r="I36" s="265" t="s">
         <v>77</v>
       </c>
-      <c r="J36" s="297"/>
-      <c r="K36" s="297"/>
-      <c r="L36" s="298"/>
+      <c r="J36" s="266"/>
+      <c r="K36" s="266"/>
+      <c r="L36" s="267"/>
     </row>
     <row r="37" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="51" t="s">
         <v>62</v>
       </c>
       <c r="B37" s="52"/>
-      <c r="C37" s="248" t="s">
+      <c r="C37" s="199" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="248"/>
-      <c r="E37" s="248"/>
-      <c r="F37" s="248"/>
+      <c r="D37" s="199"/>
+      <c r="E37" s="199"/>
+      <c r="F37" s="199"/>
       <c r="G37" s="51" t="s">
         <v>62</v>
       </c>
       <c r="H37" s="52"/>
-      <c r="I37" s="249" t="s">
+      <c r="I37" s="200" t="s">
         <v>63</v>
       </c>
-      <c r="J37" s="249"/>
-      <c r="K37" s="249"/>
-      <c r="L37" s="249"/>
+      <c r="J37" s="200"/>
+      <c r="K37" s="200"/>
+      <c r="L37" s="200"/>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
@@ -5366,6 +5366,53 @@
     </row>
   </sheetData>
   <mergeCells count="63">
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="I37:L37"/>
     <mergeCell ref="I27:L27"/>
@@ -5382,53 +5429,6 @@
     <mergeCell ref="I30:L30"/>
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="I35:L35"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
   </mergeCells>
   <conditionalFormatting sqref="E8">
     <cfRule type="expression" priority="9">
@@ -5633,10 +5633,10 @@
       <c r="A7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="328" t="s">
+      <c r="C7" s="319" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="328"/>
+      <c r="D7" s="319"/>
       <c r="E7" s="15" t="s">
         <v>29</v>
       </c>
@@ -5646,10 +5646,10 @@
       <c r="G7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="328" t="s">
+      <c r="I7" s="319" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="328"/>
+      <c r="J7" s="319"/>
       <c r="K7" s="15" t="s">
         <v>30</v>
       </c>
@@ -5681,19 +5681,19 @@
       <c r="A9" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="314" t="s">
+      <c r="C9" s="321" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="314"/>
+      <c r="D9" s="321"/>
       <c r="E9" s="43"/>
       <c r="F9" s="42"/>
       <c r="G9" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="314" t="s">
+      <c r="I9" s="321" t="s">
         <v>90</v>
       </c>
-      <c r="J9" s="314"/>
+      <c r="J9" s="321"/>
       <c r="K9" s="43"/>
       <c r="L9" s="42"/>
     </row>
@@ -5730,90 +5730,90 @@
       <c r="B11" s="24">
         <v>3</v>
       </c>
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="73" t="s">
         <v>149</v>
       </c>
-      <c r="D11" s="80"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="81"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="75"/>
       <c r="G11" s="23" t="s">
         <v>18</v>
       </c>
       <c r="H11" s="24">
         <v>3</v>
       </c>
-      <c r="I11" s="79" t="s">
+      <c r="I11" s="73" t="s">
         <v>161</v>
       </c>
-      <c r="J11" s="80"/>
-      <c r="K11" s="80"/>
-      <c r="L11" s="81"/>
+      <c r="J11" s="74"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="75"/>
     </row>
     <row r="12" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
       <c r="B12" s="26">
         <v>4</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C12" s="132" t="s">
         <v>149</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="75"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="163"/>
       <c r="G12" s="25"/>
       <c r="H12" s="26">
         <v>4</v>
       </c>
-      <c r="I12" s="73" t="s">
+      <c r="I12" s="132" t="s">
         <v>151</v>
       </c>
-      <c r="J12" s="74"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="75"/>
+      <c r="J12" s="133"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="163"/>
     </row>
     <row r="13" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
       <c r="B13" s="46">
         <v>5</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="132" t="s">
         <v>150</v>
       </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="75"/>
+      <c r="D13" s="133"/>
+      <c r="E13" s="133"/>
+      <c r="F13" s="163"/>
       <c r="G13" s="25"/>
       <c r="H13" s="26">
         <v>5</v>
       </c>
-      <c r="I13" s="73" t="s">
+      <c r="I13" s="132" t="s">
         <v>151</v>
       </c>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="75"/>
+      <c r="J13" s="133"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="163"/>
     </row>
     <row r="14" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="49"/>
       <c r="B14" s="46">
         <v>6</v>
       </c>
-      <c r="C14" s="73" t="s">
+      <c r="C14" s="132" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="75"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="163"/>
       <c r="G14" s="49"/>
       <c r="H14" s="46">
         <v>6</v>
       </c>
-      <c r="I14" s="73" t="s">
+      <c r="I14" s="132" t="s">
         <v>152</v>
       </c>
-      <c r="J14" s="74"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="75"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="163"/>
     </row>
     <row r="15" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="29" t="s">
@@ -5822,106 +5822,106 @@
       <c r="B15" s="30">
         <v>2</v>
       </c>
-      <c r="C15" s="174"/>
-      <c r="D15" s="175"/>
-      <c r="E15" s="175"/>
-      <c r="F15" s="176"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="84"/>
       <c r="G15" s="29" t="s">
         <v>19</v>
       </c>
       <c r="H15" s="30">
         <v>2</v>
       </c>
-      <c r="I15" s="119" t="s">
+      <c r="I15" s="89" t="s">
         <v>145</v>
       </c>
-      <c r="J15" s="120"/>
-      <c r="K15" s="120"/>
-      <c r="L15" s="121"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="90"/>
+      <c r="L15" s="91"/>
     </row>
     <row r="16" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
       <c r="B16" s="26">
         <v>3</v>
       </c>
-      <c r="C16" s="165" t="s">
+      <c r="C16" s="106" t="s">
         <v>144</v>
       </c>
-      <c r="D16" s="292"/>
-      <c r="E16" s="262"/>
-      <c r="F16" s="182"/>
+      <c r="D16" s="295"/>
+      <c r="E16" s="305"/>
+      <c r="F16" s="98"/>
       <c r="G16" s="25"/>
       <c r="H16" s="26">
         <v>3</v>
       </c>
-      <c r="I16" s="73" t="s">
+      <c r="I16" s="132" t="s">
         <v>153</v>
       </c>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
-      <c r="L16" s="75"/>
+      <c r="J16" s="133"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="163"/>
     </row>
     <row r="17" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="25"/>
       <c r="B17" s="26">
         <v>4</v>
       </c>
-      <c r="C17" s="165" t="s">
+      <c r="C17" s="106" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="292"/>
-      <c r="E17" s="262"/>
-      <c r="F17" s="182"/>
+      <c r="D17" s="295"/>
+      <c r="E17" s="305"/>
+      <c r="F17" s="98"/>
       <c r="G17" s="25"/>
       <c r="H17" s="26">
         <v>4</v>
       </c>
-      <c r="I17" s="73" t="s">
+      <c r="I17" s="132" t="s">
         <v>153</v>
       </c>
-      <c r="J17" s="74"/>
-      <c r="K17" s="74"/>
-      <c r="L17" s="75"/>
+      <c r="J17" s="133"/>
+      <c r="K17" s="133"/>
+      <c r="L17" s="163"/>
     </row>
     <row r="18" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="49"/>
       <c r="B18" s="46">
         <v>5</v>
       </c>
-      <c r="C18" s="313" t="s">
+      <c r="C18" s="320" t="s">
         <v>142</v>
       </c>
-      <c r="D18" s="153"/>
-      <c r="E18" s="153"/>
-      <c r="F18" s="154"/>
+      <c r="D18" s="134"/>
+      <c r="E18" s="134"/>
+      <c r="F18" s="135"/>
       <c r="G18" s="49"/>
       <c r="H18" s="46">
         <v>5</v>
       </c>
-      <c r="I18" s="313" t="s">
+      <c r="I18" s="320" t="s">
         <v>142</v>
       </c>
-      <c r="J18" s="153"/>
-      <c r="K18" s="153"/>
-      <c r="L18" s="154"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="134"/>
+      <c r="L18" s="135"/>
     </row>
     <row r="19" spans="1:12" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="31"/>
       <c r="B19" s="28">
         <v>6</v>
       </c>
-      <c r="C19" s="143"/>
-      <c r="D19" s="144"/>
-      <c r="E19" s="144"/>
-      <c r="F19" s="145"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="123"/>
+      <c r="F19" s="124"/>
       <c r="G19" s="31"/>
       <c r="H19" s="28">
         <v>6</v>
       </c>
-      <c r="I19" s="76"/>
-      <c r="J19" s="77"/>
-      <c r="K19" s="77"/>
-      <c r="L19" s="78"/>
+      <c r="I19" s="164"/>
+      <c r="J19" s="165"/>
+      <c r="K19" s="165"/>
+      <c r="L19" s="166"/>
     </row>
     <row r="20" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="29" t="s">
@@ -5930,90 +5930,90 @@
       <c r="B20" s="30">
         <v>3</v>
       </c>
-      <c r="C20" s="325" t="s">
+      <c r="C20" s="331" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="326"/>
-      <c r="E20" s="326"/>
-      <c r="F20" s="327"/>
+      <c r="D20" s="332"/>
+      <c r="E20" s="332"/>
+      <c r="F20" s="333"/>
       <c r="G20" s="29" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="30">
         <v>3</v>
       </c>
-      <c r="I20" s="293" t="s">
+      <c r="I20" s="262" t="s">
         <v>154</v>
       </c>
-      <c r="J20" s="294"/>
-      <c r="K20" s="294"/>
-      <c r="L20" s="295"/>
+      <c r="J20" s="263"/>
+      <c r="K20" s="263"/>
+      <c r="L20" s="264"/>
     </row>
     <row r="21" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="25"/>
       <c r="B21" s="26">
         <v>4</v>
       </c>
-      <c r="C21" s="99" t="s">
+      <c r="C21" s="85" t="s">
         <v>141</v>
       </c>
-      <c r="D21" s="100"/>
-      <c r="E21" s="100" t="s">
+      <c r="D21" s="86"/>
+      <c r="E21" s="86" t="s">
         <v>143</v>
       </c>
-      <c r="F21" s="101"/>
+      <c r="F21" s="92"/>
       <c r="G21" s="25"/>
       <c r="H21" s="26">
         <v>4</v>
       </c>
-      <c r="I21" s="73" t="s">
+      <c r="I21" s="132" t="s">
         <v>155</v>
       </c>
-      <c r="J21" s="74"/>
-      <c r="K21" s="74"/>
-      <c r="L21" s="75"/>
+      <c r="J21" s="133"/>
+      <c r="K21" s="133"/>
+      <c r="L21" s="163"/>
     </row>
     <row r="22" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="25"/>
       <c r="B22" s="26">
         <v>5</v>
       </c>
-      <c r="C22" s="99" t="s">
+      <c r="C22" s="85" t="s">
         <v>141</v>
       </c>
-      <c r="D22" s="100"/>
-      <c r="E22" s="100" t="s">
+      <c r="D22" s="86"/>
+      <c r="E22" s="86" t="s">
         <v>143</v>
       </c>
-      <c r="F22" s="101"/>
+      <c r="F22" s="92"/>
       <c r="G22" s="25"/>
       <c r="H22" s="26">
         <v>5</v>
       </c>
-      <c r="I22" s="73" t="s">
+      <c r="I22" s="132" t="s">
         <v>155</v>
       </c>
-      <c r="J22" s="74"/>
-      <c r="K22" s="74"/>
-      <c r="L22" s="75"/>
+      <c r="J22" s="133"/>
+      <c r="K22" s="133"/>
+      <c r="L22" s="163"/>
     </row>
     <row r="23" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="25"/>
       <c r="B23" s="26">
         <v>6</v>
       </c>
-      <c r="C23" s="299"/>
-      <c r="D23" s="300"/>
-      <c r="E23" s="300"/>
-      <c r="F23" s="301"/>
+      <c r="C23" s="268"/>
+      <c r="D23" s="269"/>
+      <c r="E23" s="269"/>
+      <c r="F23" s="270"/>
       <c r="G23" s="25"/>
       <c r="H23" s="26">
         <v>6</v>
       </c>
-      <c r="I23" s="155"/>
-      <c r="J23" s="156"/>
-      <c r="K23" s="156"/>
-      <c r="L23" s="157"/>
+      <c r="I23" s="136"/>
+      <c r="J23" s="137"/>
+      <c r="K23" s="137"/>
+      <c r="L23" s="138"/>
     </row>
     <row r="24" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="29" t="s">
@@ -6022,86 +6022,86 @@
       <c r="B24" s="30">
         <v>2</v>
       </c>
-      <c r="C24" s="330"/>
-      <c r="D24" s="331"/>
-      <c r="E24" s="332" t="s">
+      <c r="C24" s="311"/>
+      <c r="D24" s="312"/>
+      <c r="E24" s="313" t="s">
         <v>156</v>
       </c>
-      <c r="F24" s="279"/>
+      <c r="F24" s="294"/>
       <c r="G24" s="29" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="30">
         <v>2</v>
       </c>
-      <c r="I24" s="308"/>
-      <c r="J24" s="309"/>
-      <c r="K24" s="309"/>
-      <c r="L24" s="310"/>
+      <c r="I24" s="334"/>
+      <c r="J24" s="335"/>
+      <c r="K24" s="335"/>
+      <c r="L24" s="336"/>
     </row>
     <row r="25" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="25"/>
       <c r="B25" s="26">
         <v>3</v>
       </c>
-      <c r="C25" s="155"/>
-      <c r="D25" s="318"/>
-      <c r="E25" s="319" t="s">
+      <c r="C25" s="136"/>
+      <c r="D25" s="325"/>
+      <c r="E25" s="318" t="s">
         <v>156</v>
       </c>
-      <c r="F25" s="75"/>
+      <c r="F25" s="163"/>
       <c r="G25" s="25"/>
       <c r="H25" s="26">
         <v>3</v>
       </c>
-      <c r="I25" s="73"/>
-      <c r="J25" s="74"/>
-      <c r="K25" s="74"/>
-      <c r="L25" s="75"/>
+      <c r="I25" s="132"/>
+      <c r="J25" s="133"/>
+      <c r="K25" s="133"/>
+      <c r="L25" s="163"/>
     </row>
     <row r="26" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="25"/>
       <c r="B26" s="26">
         <v>4</v>
       </c>
-      <c r="C26" s="73" t="s">
+      <c r="C26" s="132" t="s">
         <v>152</v>
       </c>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="75"/>
+      <c r="D26" s="133"/>
+      <c r="E26" s="133"/>
+      <c r="F26" s="163"/>
       <c r="G26" s="25"/>
       <c r="H26" s="26">
         <v>4</v>
       </c>
-      <c r="I26" s="73" t="s">
+      <c r="I26" s="132" t="s">
         <v>152</v>
       </c>
-      <c r="J26" s="74"/>
-      <c r="K26" s="74"/>
-      <c r="L26" s="75"/>
+      <c r="J26" s="133"/>
+      <c r="K26" s="133"/>
+      <c r="L26" s="163"/>
     </row>
     <row r="27" spans="1:12" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="25"/>
       <c r="B27" s="26">
         <v>5</v>
       </c>
-      <c r="C27" s="177" t="s">
+      <c r="C27" s="93" t="s">
         <v>142</v>
       </c>
-      <c r="D27" s="178"/>
-      <c r="E27" s="178"/>
-      <c r="F27" s="179"/>
+      <c r="D27" s="94"/>
+      <c r="E27" s="94"/>
+      <c r="F27" s="95"/>
       <c r="G27" s="25"/>
       <c r="H27" s="26">
         <v>5</v>
       </c>
-      <c r="I27" s="177" t="s">
+      <c r="I27" s="93" t="s">
         <v>142</v>
       </c>
-      <c r="J27" s="178"/>
-      <c r="K27" s="178"/>
-      <c r="L27" s="179"/>
+      <c r="J27" s="94"/>
+      <c r="K27" s="94"/>
+      <c r="L27" s="95"/>
     </row>
     <row r="28" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="29" t="s">
@@ -6110,110 +6110,110 @@
       <c r="B28" s="30">
         <v>1</v>
       </c>
-      <c r="C28" s="323" t="s">
+      <c r="C28" s="329" t="s">
         <v>139</v>
       </c>
-      <c r="D28" s="324"/>
-      <c r="E28" s="311"/>
-      <c r="F28" s="312"/>
+      <c r="D28" s="330"/>
+      <c r="E28" s="337"/>
+      <c r="F28" s="338"/>
       <c r="G28" s="29" t="s">
         <v>22</v>
       </c>
       <c r="H28" s="30">
         <v>2</v>
       </c>
-      <c r="I28" s="174"/>
-      <c r="J28" s="175"/>
-      <c r="K28" s="175"/>
-      <c r="L28" s="176"/>
+      <c r="I28" s="82"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="84"/>
     </row>
     <row r="29" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="32"/>
       <c r="B29" s="26">
         <v>2</v>
       </c>
-      <c r="C29" s="99" t="s">
+      <c r="C29" s="85" t="s">
         <v>139</v>
       </c>
-      <c r="D29" s="100"/>
-      <c r="E29" s="100" t="s">
+      <c r="D29" s="86"/>
+      <c r="E29" s="86" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="101"/>
+      <c r="F29" s="92"/>
       <c r="G29" s="32"/>
       <c r="H29" s="26">
         <v>3</v>
       </c>
-      <c r="I29" s="155"/>
-      <c r="J29" s="156"/>
-      <c r="K29" s="156"/>
-      <c r="L29" s="157"/>
+      <c r="I29" s="136"/>
+      <c r="J29" s="137"/>
+      <c r="K29" s="137"/>
+      <c r="L29" s="138"/>
     </row>
     <row r="30" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="32"/>
       <c r="B30" s="26">
         <v>3</v>
       </c>
-      <c r="C30" s="99" t="s">
+      <c r="C30" s="85" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="100"/>
-      <c r="E30" s="100" t="s">
+      <c r="D30" s="86"/>
+      <c r="E30" s="86" t="s">
         <v>140</v>
       </c>
-      <c r="F30" s="101"/>
+      <c r="F30" s="92"/>
       <c r="G30" s="32"/>
       <c r="H30" s="26">
         <v>4</v>
       </c>
-      <c r="I30" s="99"/>
-      <c r="J30" s="100"/>
-      <c r="K30" s="100"/>
-      <c r="L30" s="101"/>
+      <c r="I30" s="85"/>
+      <c r="J30" s="86"/>
+      <c r="K30" s="86"/>
+      <c r="L30" s="92"/>
     </row>
     <row r="31" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="50"/>
       <c r="B31" s="46">
         <v>4</v>
       </c>
-      <c r="C31" s="73" t="s">
+      <c r="C31" s="132" t="s">
         <v>146</v>
       </c>
-      <c r="D31" s="329"/>
-      <c r="E31" s="319" t="s">
+      <c r="D31" s="317"/>
+      <c r="E31" s="318" t="s">
         <v>140</v>
       </c>
-      <c r="F31" s="75"/>
+      <c r="F31" s="163"/>
       <c r="G31" s="50"/>
       <c r="H31" s="46">
         <v>5</v>
       </c>
-      <c r="I31" s="99" t="s">
+      <c r="I31" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="J31" s="100"/>
-      <c r="K31" s="100"/>
-      <c r="L31" s="101"/>
+      <c r="J31" s="86"/>
+      <c r="K31" s="86"/>
+      <c r="L31" s="92"/>
     </row>
     <row r="32" spans="1:12" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="34"/>
       <c r="B32" s="28">
         <v>5</v>
       </c>
-      <c r="C32" s="333"/>
-      <c r="D32" s="334"/>
-      <c r="E32" s="334"/>
-      <c r="F32" s="335"/>
+      <c r="C32" s="314"/>
+      <c r="D32" s="315"/>
+      <c r="E32" s="315"/>
+      <c r="F32" s="316"/>
       <c r="G32" s="34"/>
       <c r="H32" s="28">
         <v>6</v>
       </c>
-      <c r="I32" s="76" t="s">
+      <c r="I32" s="164" t="s">
         <v>145</v>
       </c>
-      <c r="J32" s="77"/>
-      <c r="K32" s="77"/>
-      <c r="L32" s="78"/>
+      <c r="J32" s="165"/>
+      <c r="K32" s="165"/>
+      <c r="L32" s="166"/>
     </row>
     <row r="33" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="44" t="s">
@@ -6222,108 +6222,108 @@
       <c r="B33" s="30">
         <v>1</v>
       </c>
-      <c r="C33" s="336"/>
-      <c r="D33" s="337"/>
-      <c r="E33" s="337"/>
-      <c r="F33" s="338"/>
+      <c r="C33" s="308"/>
+      <c r="D33" s="309"/>
+      <c r="E33" s="309"/>
+      <c r="F33" s="310"/>
       <c r="G33" s="44" t="s">
         <v>23</v>
       </c>
       <c r="H33" s="30">
         <v>1</v>
       </c>
-      <c r="I33" s="79" t="s">
+      <c r="I33" s="73" t="s">
         <v>147</v>
       </c>
-      <c r="J33" s="80"/>
-      <c r="K33" s="80"/>
-      <c r="L33" s="81"/>
+      <c r="J33" s="74"/>
+      <c r="K33" s="74"/>
+      <c r="L33" s="75"/>
     </row>
     <row r="34" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="32"/>
       <c r="B34" s="26">
         <v>2</v>
       </c>
-      <c r="C34" s="99" t="s">
+      <c r="C34" s="85" t="s">
         <v>157</v>
       </c>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="101"/>
+      <c r="D34" s="86"/>
+      <c r="E34" s="86"/>
+      <c r="F34" s="92"/>
       <c r="G34" s="32"/>
       <c r="H34" s="26">
         <v>2</v>
       </c>
-      <c r="I34" s="73" t="s">
+      <c r="I34" s="132" t="s">
         <v>157</v>
       </c>
-      <c r="J34" s="74"/>
-      <c r="K34" s="74"/>
-      <c r="L34" s="75"/>
+      <c r="J34" s="133"/>
+      <c r="K34" s="133"/>
+      <c r="L34" s="163"/>
     </row>
     <row r="35" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="50"/>
       <c r="B35" s="26">
         <v>3</v>
       </c>
-      <c r="C35" s="99" t="s">
+      <c r="C35" s="85" t="s">
         <v>157</v>
       </c>
-      <c r="D35" s="100"/>
-      <c r="E35" s="100"/>
-      <c r="F35" s="101"/>
+      <c r="D35" s="86"/>
+      <c r="E35" s="86"/>
+      <c r="F35" s="92"/>
       <c r="G35" s="50"/>
       <c r="H35" s="26">
         <v>3</v>
       </c>
-      <c r="I35" s="73" t="s">
+      <c r="I35" s="132" t="s">
         <v>157</v>
       </c>
-      <c r="J35" s="74"/>
-      <c r="K35" s="74"/>
-      <c r="L35" s="75"/>
+      <c r="J35" s="133"/>
+      <c r="K35" s="133"/>
+      <c r="L35" s="163"/>
     </row>
     <row r="36" spans="1:12" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="45"/>
       <c r="B36" s="28">
         <v>4</v>
       </c>
-      <c r="C36" s="299"/>
-      <c r="D36" s="300"/>
-      <c r="E36" s="160" t="s">
+      <c r="C36" s="268"/>
+      <c r="D36" s="269"/>
+      <c r="E36" s="116" t="s">
         <v>148</v>
       </c>
-      <c r="F36" s="161"/>
+      <c r="F36" s="117"/>
       <c r="G36" s="45"/>
       <c r="H36" s="28">
         <v>4</v>
       </c>
-      <c r="I36" s="155"/>
-      <c r="J36" s="156"/>
-      <c r="K36" s="156"/>
-      <c r="L36" s="157"/>
+      <c r="I36" s="136"/>
+      <c r="J36" s="137"/>
+      <c r="K36" s="137"/>
+      <c r="L36" s="138"/>
     </row>
     <row r="37" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="71"/>
       <c r="B37" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="320" t="s">
+      <c r="C37" s="326" t="s">
         <v>103</v>
       </c>
-      <c r="D37" s="321"/>
-      <c r="E37" s="321"/>
-      <c r="F37" s="322"/>
+      <c r="D37" s="327"/>
+      <c r="E37" s="327"/>
+      <c r="F37" s="328"/>
       <c r="G37" s="71"/>
       <c r="H37" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="I37" s="315" t="s">
+      <c r="I37" s="322" t="s">
         <v>103</v>
       </c>
-      <c r="J37" s="316"/>
-      <c r="K37" s="316"/>
-      <c r="L37" s="317"/>
+      <c r="J37" s="323"/>
+      <c r="K37" s="323"/>
+      <c r="L37" s="324"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
@@ -6355,21 +6355,43 @@
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="C20:F20"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="I11:L11"/>
     <mergeCell ref="I12:L12"/>
@@ -6386,44 +6408,22 @@
     <mergeCell ref="I15:L15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="I31:L31"/>
     <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E9">
     <cfRule type="expression" priority="8">
